--- a/引脚对应表2.xlsx
+++ b/引脚对应表2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\11清华云盘资料库\大二\电设\vscode-esp32s3_testcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D36E83A-2524-47B2-82EF-DC623A80EDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F7139B-932D-400F-805D-0DA0875B2A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51" yWindow="189" windowWidth="10483" windowHeight="12325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,13 +175,7 @@
     <t>GND</t>
   </si>
   <si>
-    <t>GPIO40</t>
-  </si>
-  <si>
     <t>Trig(接收高电平后触发测距信号)</t>
-  </si>
-  <si>
-    <t>GPIO39</t>
   </si>
   <si>
     <t>Echo(高电平持续时间正比于超声波往返时间，回响信号输出)</t>
@@ -255,6 +249,14 @@
   </si>
   <si>
     <t>GPIO43</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO46</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -900,20 +902,20 @@
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="C31" s="5"/>
-    </row>
-    <row r="32" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="C32" s="3"/>
     </row>
@@ -927,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="3"/>
     </row>
@@ -942,19 +944,19 @@
     </row>
     <row r="36" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37" s="5"/>
     </row>
@@ -968,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39" s="5"/>
     </row>
@@ -990,46 +992,46 @@
     </row>
     <row r="42" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C46" s="3"/>
     </row>
@@ -1043,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C48" s="3"/>
     </row>
@@ -1059,7 +1061,7 @@
     <row r="50" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C50" s="3"/>
     </row>
@@ -1073,35 +1075,35 @@
         <v>0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C56" s="3"/>
     </row>

--- a/引脚对应表2.xlsx
+++ b/引脚对应表2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\11清华云盘资料库\大二\电设\vscode-esp32s3_testcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F7139B-932D-400F-805D-0DA0875B2A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03785D3A-B693-4FFF-BACC-AA6B3508D0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51" yWindow="189" windowWidth="10483" windowHeight="12325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>ESP32-S3 DevKitC-1</t>
   </si>
@@ -115,13 +115,7 @@
     <t>摄像机信号</t>
   </si>
   <si>
-    <t>GPIO11</t>
-  </si>
-  <si>
     <t>PAN_SIG（水平舵机）</t>
-  </si>
-  <si>
-    <t>GPIO18</t>
   </si>
   <si>
     <t>TILT_SIG（垂直舵机）</t>
@@ -252,11 +246,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>GPIO3</t>
+    <t>GPIO</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>GPIO46</t>
+    <t>GPIO11</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO18</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -781,38 +779,38 @@
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5"/>
     </row>
@@ -831,43 +829,43 @@
         <v>0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3"/>
     </row>
@@ -881,14 +879,14 @@
         <v>0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5">
         <v>3.3</v>
@@ -897,7 +895,7 @@
     <row r="30" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -906,16 +904,16 @@
         <v>70</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3"/>
     </row>
@@ -929,14 +927,14 @@
         <v>0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="5">
         <v>3.3</v>
@@ -944,19 +942,19 @@
     </row>
     <row r="36" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" s="5"/>
     </row>
@@ -970,14 +968,14 @@
         <v>0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3">
         <v>3.3</v>
@@ -986,52 +984,52 @@
     <row r="41" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C46" s="3"/>
     </row>
@@ -1045,14 +1043,14 @@
         <v>0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C49" s="5">
         <v>3.3</v>
@@ -1061,7 +1059,7 @@
     <row r="50" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50" s="3"/>
     </row>
@@ -1075,35 +1073,35 @@
         <v>0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C56" s="3"/>
     </row>

--- a/引脚对应表2.xlsx
+++ b/引脚对应表2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\11清华云盘资料库\大二\电设\vscode-esp32s3_testcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEC113F-B2B8-4C46-89C2-BF7E82BB6D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C181FDE9-61DB-478D-8011-7DFA528B94FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="437" windowWidth="11023" windowHeight="12326" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>ESP32-S3 DevKitC-1</t>
   </si>
@@ -88,165 +88,204 @@
     <t>AIN2</t>
   </si>
   <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>GPIO16</t>
+  </si>
+  <si>
+    <t>PWMD</t>
+  </si>
+  <si>
+    <t>GPIO7</t>
+  </si>
+  <si>
+    <t>DIN1</t>
+  </si>
+  <si>
+    <t>DIN2</t>
+  </si>
+  <si>
+    <t>摄像机信号</t>
+  </si>
+  <si>
+    <t>PAN_SIG（水平舵机）</t>
+  </si>
+  <si>
+    <t>TILT_SIG（垂直舵机）</t>
+  </si>
+  <si>
+    <t>GPIO20</t>
+  </si>
+  <si>
+    <t>USB_D+</t>
+  </si>
+  <si>
+    <t>GPIO19</t>
+  </si>
+  <si>
+    <t>USB_D-</t>
+  </si>
+  <si>
+    <t>四路红外检测模块</t>
+  </si>
+  <si>
+    <t>OUT1</t>
+  </si>
+  <si>
+    <t>OUT2</t>
+  </si>
+  <si>
+    <t>OUT3</t>
+  </si>
+  <si>
+    <t>OUT4</t>
+  </si>
+  <si>
+    <t>超声波模块</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>Trig(接收高电平后触发测距信号)</t>
+  </si>
+  <si>
+    <t>Echo(高电平持续时间正比于超声波往返时间，回响信号输出)</t>
+  </si>
+  <si>
+    <t>串口转USB模块</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>RX</t>
+  </si>
+  <si>
+    <t>显示屏模块</t>
+  </si>
+  <si>
+    <t>SCK(硬件 SPI2 时钟引脚，推荐 20~40MHz，刷屏流畅不闪)</t>
+  </si>
+  <si>
+    <t>SDI(硬件 SPI2 主机输出，单向发送命令和像素数据)</t>
+  </si>
+  <si>
+    <t>D/C电平(数据 / 命令切换，高低电平切换即可)</t>
+  </si>
+  <si>
+    <t>CS(片选控制；单屏使用也可直接接地，省一个引脚)</t>
+  </si>
+  <si>
+    <t>RST(屏幕死机的时候用来重启，上电时序需要拉低再拉高)</t>
+  </si>
+  <si>
+    <t>温湿度传感器</t>
+  </si>
+  <si>
+    <t>DATA(数字输出接单片机I/O直接显示温湿度)</t>
+  </si>
+  <si>
+    <t>陀螺仪模块</t>
+  </si>
+  <si>
+    <t>INT(中断，停止工作)</t>
+  </si>
+  <si>
+    <t>AD0(地址)</t>
+  </si>
+  <si>
+    <t>SDA(数据）</t>
+  </si>
+  <si>
+    <t>SCL(时钟）</t>
+  </si>
+  <si>
+    <t>GPIO1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO13</t>
+  </si>
+  <si>
+    <t>GPIO14</t>
+  </si>
+  <si>
+    <t>GPIO21</t>
+  </si>
+  <si>
+    <t>GPIO47</t>
+  </si>
+  <si>
+    <t>GPIO38</t>
+  </si>
+  <si>
+    <t>GPIO18</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO11</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO15</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO39</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO40</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO41</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO42</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>GPIO17</t>
-  </si>
-  <si>
-    <t>ADC</t>
-  </si>
-  <si>
-    <t>GPIO16</t>
-  </si>
-  <si>
-    <t>PWMD</t>
-  </si>
-  <si>
-    <t>GPIO7</t>
-  </si>
-  <si>
-    <t>DIN1</t>
-  </si>
-  <si>
-    <t>GPIO15</t>
-  </si>
-  <si>
-    <t>DIN2</t>
-  </si>
-  <si>
-    <t>摄像机信号</t>
-  </si>
-  <si>
-    <t>PAN_SIG（水平舵机）</t>
-  </si>
-  <si>
-    <t>TILT_SIG（垂直舵机）</t>
-  </si>
-  <si>
-    <t>GPIO20</t>
-  </si>
-  <si>
-    <t>USB_D+</t>
-  </si>
-  <si>
-    <t>GPIO19</t>
-  </si>
-  <si>
-    <t>USB_D-</t>
-  </si>
-  <si>
-    <t>四路红外检测模块</t>
-  </si>
-  <si>
-    <t>GPIO41</t>
-  </si>
-  <si>
-    <t>OUT1</t>
-  </si>
-  <si>
-    <t>GPIO42</t>
-  </si>
-  <si>
-    <t>OUT2</t>
-  </si>
-  <si>
-    <t>GPIO2</t>
-  </si>
-  <si>
-    <t>OUT3</t>
-  </si>
-  <si>
-    <t>OUT4</t>
-  </si>
-  <si>
-    <t>超声波模块</t>
-  </si>
-  <si>
-    <t>VCC</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>Trig(接收高电平后触发测距信号)</t>
-  </si>
-  <si>
-    <t>Echo(高电平持续时间正比于超声波往返时间，回响信号输出)</t>
-  </si>
-  <si>
-    <t>串口转USB模块</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>RX</t>
-  </si>
-  <si>
-    <t>显示屏模块</t>
-  </si>
-  <si>
-    <t>SCK(硬件 SPI2 时钟引脚，推荐 20~40MHz，刷屏流畅不闪)</t>
-  </si>
-  <si>
-    <t>SDI(硬件 SPI2 主机输出，单向发送命令和像素数据)</t>
-  </si>
-  <si>
-    <t>D/C电平(数据 / 命令切换，高低电平切换即可)</t>
-  </si>
-  <si>
-    <t>CS(片选控制；单屏使用也可直接接地，省一个引脚)</t>
-  </si>
-  <si>
-    <t>RST(屏幕死机的时候用来重启，上电时序需要拉低再拉高)</t>
-  </si>
-  <si>
-    <t>温湿度传感器</t>
-  </si>
-  <si>
-    <t>DATA(数字输出接单片机I/O直接显示温湿度)</t>
-  </si>
-  <si>
-    <t>陀螺仪模块</t>
-  </si>
-  <si>
-    <t>INT(中断，停止工作)</t>
-  </si>
-  <si>
-    <t>AD0(地址)</t>
-  </si>
-  <si>
-    <t>SDA(数据）</t>
-  </si>
-  <si>
-    <t>SCL(时钟）</t>
-  </si>
-  <si>
-    <t>GPIO1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GPIO2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GPIO40</t>
-  </si>
-  <si>
-    <t>GPIO39</t>
-  </si>
-  <si>
-    <t>GPIO13</t>
-  </si>
-  <si>
-    <t>GPIO14</t>
-  </si>
-  <si>
-    <t>GPIO21</t>
-  </si>
-  <si>
-    <t>GPIO47</t>
-  </si>
-  <si>
-    <t>GPIO38</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -639,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.4609375" customWidth="1"/>
@@ -720,94 +759,96 @@
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="C9" s="9"/>
     </row>
     <row r="10" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
+      <c r="A14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>0</v>
+      <c r="A15" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="6"/>
+      <c r="A16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>61</v>
+      <c r="A17" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C17" s="9"/>
     </row>
     <row r="18" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="6"/>
+      <c r="A18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="A19" s="9"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
@@ -816,53 +857,53 @@
       <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>0</v>
+      <c r="A22" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C25" s="9"/>
     </row>
     <row r="26" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
@@ -875,41 +916,35 @@
         <v>0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="9">
-        <v>3.3</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
-        <v>62</v>
-      </c>
+      <c r="A31" s="7"/>
       <c r="B31" s="8" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>63</v>
-      </c>
+      <c r="A32" s="4"/>
       <c r="B32" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C32" s="6"/>
     </row>
@@ -923,181 +958,187 @@
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C35" s="9">
         <v>3.3</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A36" s="4"/>
       <c r="B36" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C36" s="6"/>
     </row>
     <row r="37" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>46</v>
+      <c r="A37" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C37" s="9"/>
     </row>
     <row r="38" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="5"/>
+      <c r="A38" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="C38" s="6"/>
     </row>
     <row r="39" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="9"/>
+    </row>
+    <row r="40" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="9"/>
-    </row>
-    <row r="40" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
       <c r="B40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="6"/>
+    </row>
+    <row r="41" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="6">
+      <c r="B42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="9"/>
+    </row>
+    <row r="44" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="9"/>
+    </row>
+    <row r="46" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="6">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="9"/>
-    </row>
-    <row r="42" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="6"/>
-    </row>
-    <row r="43" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="9"/>
-    </row>
-    <row r="44" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="6"/>
-    </row>
-    <row r="45" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A45" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="9"/>
-    </row>
-    <row r="46" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="6"/>
     </row>
     <row r="47" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
-      <c r="B47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="C47" s="9"/>
     </row>
     <row r="48" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>0</v>
+      <c r="A48" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="9">
-        <v>3.3</v>
-      </c>
+      <c r="A49" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="9"/>
     </row>
     <row r="50" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
+      <c r="A50" s="14" t="s">
+        <v>59</v>
+      </c>
       <c r="B50" s="5" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C50" s="6"/>
     </row>
     <row r="51" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
+      <c r="A51" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="C51" s="9"/>
     </row>
     <row r="52" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>55</v>
+      <c r="A52" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C52" s="6"/>
     </row>
     <row r="53" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
-      <c r="B53" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="B53" s="8"/>
       <c r="C53" s="9"/>
     </row>
     <row r="54" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
-        <v>57</v>
+      <c r="A54" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C54" s="6"/>
     </row>
     <row r="55" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
-      <c r="B55" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="9"/>
+      <c r="B55" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="9">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="56" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
-      <c r="B56" s="6" t="s">
-        <v>59</v>
+      <c r="B56" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C56" s="6"/>
     </row>
@@ -1107,28 +1148,40 @@
       <c r="C57" s="9"/>
     </row>
     <row r="58" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="C58" s="6"/>
     </row>
     <row r="59" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
+      <c r="B59" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="C59" s="9"/>
     </row>
     <row r="60" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="B60" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="C60" s="6"/>
     </row>
     <row r="61" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
+      <c r="B61" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="C61" s="9"/>
     </row>
     <row r="62" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
+      <c r="B62" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="C62" s="6"/>
     </row>
     <row r="63" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
@@ -1152,7 +1205,37 @@
       <c r="C66" s="6"/>
     </row>
     <row r="67" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
-      <c r="B67" s="6"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+    </row>
+    <row r="69" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+    </row>
+    <row r="70" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+    </row>
+    <row r="71" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A71" s="9"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+    </row>
+    <row r="72" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+    </row>
+    <row r="73" spans="1:3" ht="16.3" x14ac:dyDescent="0.3">
+      <c r="B73" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
